--- a/기초데이터/원본/15. 커튼월창.xlsx
+++ b/기초데이터/원본/15. 커튼월창.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\5. 연구과제\54. 기존건물에너지리모델링\04.4차년도\05.오프라인툴\3.송신\1.DB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Remodeling_SW\기초데이터\원본\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="10305" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="10305" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="커튼월창프레임" sheetId="7" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="이미지_설치열교" sheetId="19" r:id="rId6"/>
     <sheet name="이미지_구조유형" sheetId="14" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -112,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="222">
   <si>
     <t>내단열</t>
   </si>
@@ -1144,6 +1147,59 @@
   <si>
     <t>단위</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>중간</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내부측</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>외단열</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>외부측</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/CWInstall/image4.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/CWInstall/image5.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image6.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image7.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image8.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image9.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image10.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image11.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image12.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image13.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image14.png</t>
+  </si>
+  <si>
+    <t>images/CWInstall/image15.png</t>
   </si>
 </sst>
 </file>
@@ -2165,1595 +2221,6 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>646232</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000021000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="285750"/>
-          <a:ext cx="646232" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>664522</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="1724025"/>
-          <a:ext cx="664522" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>768163</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000023000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="3162300"/>
-          <a:ext cx="768163" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>646232</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000021000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="4600575"/>
-          <a:ext cx="646232" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>664522</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="6038850"/>
-          <a:ext cx="664522" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>768163</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="그림 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000023000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="7477125"/>
-          <a:ext cx="768163" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>646232</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="그림 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000021000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="8915400"/>
-          <a:ext cx="646232" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>664522</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="그림 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="10353675"/>
-          <a:ext cx="664522" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>768163</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="그림 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000023000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="11791950"/>
-          <a:ext cx="768163" cy="1450974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>646232</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="그림 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000024000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="13230225"/>
-          <a:ext cx="646232" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>658425</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="그림 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="14668500"/>
-          <a:ext cx="658425" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>652329</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="그림 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="16106775"/>
-          <a:ext cx="652329" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>646232</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="그림 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000024000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="17545050"/>
-          <a:ext cx="646232" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>658425</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="그림 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="18983325"/>
-          <a:ext cx="658425" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>652329</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="그림 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="20421600"/>
-          <a:ext cx="652329" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>646232</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="그림 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000024000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="21859875"/>
-          <a:ext cx="646232" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>658425</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="그림 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="23298150"/>
-          <a:ext cx="658425" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>652329</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="그림 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="24736425"/>
-          <a:ext cx="652329" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>658425</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="그림 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000027000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="26174700"/>
-          <a:ext cx="658425" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>664522</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="그림 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000028000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="27612975"/>
-          <a:ext cx="664522" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>658425</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="그림 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000027000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="30489525"/>
-          <a:ext cx="658425" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>664522</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="그림 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000028000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="31927800"/>
-          <a:ext cx="664522" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>658425</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="그림 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000027000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="34804350"/>
-          <a:ext cx="658425" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>664522</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="그림 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000028000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="36242625"/>
-          <a:ext cx="664522" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>121236</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="그림 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000029000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="29051250"/>
-          <a:ext cx="902286" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>121236</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="그림 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000029000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="33366075"/>
-          <a:ext cx="902286" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>121236</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>18795</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="그림 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000029000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="37680900"/>
-          <a:ext cx="902286" cy="1457070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>609653</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="그림 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="39119175"/>
-          <a:ext cx="609653" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>652329</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="그림 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="40557450"/>
-          <a:ext cx="652329" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>72464</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="그림 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="41995725"/>
-          <a:ext cx="853514" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>609653</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="그림 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="43434000"/>
-          <a:ext cx="609653" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>652329</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="그림 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="44872275"/>
-          <a:ext cx="652329" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>72464</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="그림 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="46310550"/>
-          <a:ext cx="853514" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>609653</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="그림 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="47748825"/>
-          <a:ext cx="609653" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>652329</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="그림 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="49187100"/>
-          <a:ext cx="652329" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>72464</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>24892</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="그림 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="50625375"/>
-          <a:ext cx="853514" cy="1463167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -3874,6 +2341,241 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="메인"/>
+      <sheetName val="건물정보"/>
+      <sheetName val="건물정보생성"/>
+      <sheetName val="메인index"/>
+      <sheetName val="건물index"/>
+      <sheetName val="커튼월리스트"/>
+      <sheetName val="구조체_커튼월"/>
+      <sheetName val="커튼월추가정보"/>
+      <sheetName val="커튼월생성"/>
+      <sheetName val="커튼월입력"/>
+      <sheetName val="커튼월index"/>
+      <sheetName val="커튼월치수정보"/>
+      <sheetName val="커튼월자재DB"/>
+      <sheetName val="커튼월자재이미지"/>
+      <sheetName val="외벽리스트"/>
+      <sheetName val="구조체_외벽"/>
+      <sheetName val="열교_외벽"/>
+      <sheetName val="외벽생성"/>
+      <sheetName val="외벽index"/>
+      <sheetName val="외벽열교DB"/>
+      <sheetName val="외벽열교이미지"/>
+      <sheetName val="지붕리스트"/>
+      <sheetName val="구조체_지붕"/>
+      <sheetName val="열교_지붕"/>
+      <sheetName val="지붕생성"/>
+      <sheetName val="지붕index"/>
+      <sheetName val="지붕열교DB"/>
+      <sheetName val="지붕열교이미지"/>
+      <sheetName val="바닥리스트"/>
+      <sheetName val="구조체_바닥"/>
+      <sheetName val="열교_바닥"/>
+      <sheetName val="바닥생성"/>
+      <sheetName val="바닥열교DB"/>
+      <sheetName val="바닥index"/>
+      <sheetName val="바닥열교이미지"/>
+      <sheetName val="창호리스트"/>
+      <sheetName val="구조체_창호"/>
+      <sheetName val="창호생성"/>
+      <sheetName val="프레임계산"/>
+      <sheetName val="창호치수정보"/>
+      <sheetName val="창호입력"/>
+      <sheetName val="창호자재DB"/>
+      <sheetName val="창호index"/>
+      <sheetName val="창호자재이미지"/>
+      <sheetName val="출입문리스트"/>
+      <sheetName val="구조체_출입문"/>
+      <sheetName val="출입문생성"/>
+      <sheetName val="출입문index"/>
+      <sheetName val="출입문자재DB"/>
+      <sheetName val="출입문자재이미지"/>
+      <sheetName val="3D모델"/>
+      <sheetName val="음영"/>
+      <sheetName val="차양"/>
+      <sheetName val="차양이미지"/>
+      <sheetName val="음영차양생성"/>
+      <sheetName val="층리스트"/>
+      <sheetName val="존리스트"/>
+      <sheetName val="존일반"/>
+      <sheetName val="존index"/>
+      <sheetName val="축열기밀"/>
+      <sheetName val="외피index"/>
+      <sheetName val="용도프로필"/>
+      <sheetName val="비냉난방존내벽"/>
+      <sheetName val="01.건물"/>
+      <sheetName val="02.패시브기술_외벽"/>
+      <sheetName val="부록A.존"/>
+      <sheetName val="02.패시브기술_창호"/>
+      <sheetName val="건물모델링_기존"/>
+      <sheetName val="존외피생성"/>
+      <sheetName val="존입력"/>
+      <sheetName val="존생성"/>
+      <sheetName val="존생성_법규"/>
+      <sheetName val="InputData"/>
+      <sheetName val="Calculation"/>
+      <sheetName val="OutputData"/>
+      <sheetName val="난방설비데이터"/>
+      <sheetName val="냉방설비데이터"/>
+      <sheetName val="월별기후데이터"/>
+      <sheetName val="열전도율DB"/>
+      <sheetName val="Data"/>
+      <sheetName val="존일반index"/>
+      <sheetName val="용도프로필index"/>
+      <sheetName val="외피창호index"/>
+      <sheetName val="용도_수정"/>
+      <sheetName val="기후"/>
+      <sheetName val="기후_부하"/>
+      <sheetName val="기후_시간별"/>
+      <sheetName val="리모델링전"/>
+      <sheetName val="약산"/>
+      <sheetName val="존외피생성_법규"/>
+      <sheetName val="InputData_법규"/>
+      <sheetName val="Calculation_법규"/>
+      <sheetName val="OutputData_법규"/>
+      <sheetName val="난방설비데이터_법규"/>
+      <sheetName val="냉방설비데이터_법규"/>
+      <sheetName val="난방설비입력값_법규"/>
+      <sheetName val="대안검토_법규"/>
+      <sheetName val="00.진단"/>
+      <sheetName val="건물모델링_계획"/>
+      <sheetName val="음영_계획"/>
+      <sheetName val="차양_계획"/>
+      <sheetName val="음영차양생성_계획"/>
+      <sheetName val="존생성_계획"/>
+      <sheetName val="존외피생성_계획"/>
+      <sheetName val="InputData_계획"/>
+      <sheetName val="Calculation_계획"/>
+      <sheetName val="OutputData_계획"/>
+      <sheetName val="난방설비데이터_계획"/>
+      <sheetName val="냉방설비데이터_계획"/>
+      <sheetName val="대안검토_계획"/>
+      <sheetName val="난방설비입력값_계획"/>
+      <sheetName val="01.계획"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+      <sheetData sheetId="48"/>
+      <sheetData sheetId="49"/>
+      <sheetData sheetId="50"/>
+      <sheetData sheetId="51"/>
+      <sheetData sheetId="52"/>
+      <sheetData sheetId="53"/>
+      <sheetData sheetId="54"/>
+      <sheetData sheetId="55"/>
+      <sheetData sheetId="56"/>
+      <sheetData sheetId="57"/>
+      <sheetData sheetId="58"/>
+      <sheetData sheetId="59"/>
+      <sheetData sheetId="60"/>
+      <sheetData sheetId="61"/>
+      <sheetData sheetId="62"/>
+      <sheetData sheetId="63"/>
+      <sheetData sheetId="64"/>
+      <sheetData sheetId="65"/>
+      <sheetData sheetId="66"/>
+      <sheetData sheetId="67"/>
+      <sheetData sheetId="68"/>
+      <sheetData sheetId="69"/>
+      <sheetData sheetId="70"/>
+      <sheetData sheetId="71"/>
+      <sheetData sheetId="72"/>
+      <sheetData sheetId="73"/>
+      <sheetData sheetId="74"/>
+      <sheetData sheetId="75"/>
+      <sheetData sheetId="76"/>
+      <sheetData sheetId="77"/>
+      <sheetData sheetId="78"/>
+      <sheetData sheetId="79"/>
+      <sheetData sheetId="80"/>
+      <sheetData sheetId="81"/>
+      <sheetData sheetId="82"/>
+      <sheetData sheetId="83"/>
+      <sheetData sheetId="84"/>
+      <sheetData sheetId="85"/>
+      <sheetData sheetId="86"/>
+      <sheetData sheetId="87"/>
+      <sheetData sheetId="88"/>
+      <sheetData sheetId="89"/>
+      <sheetData sheetId="90"/>
+      <sheetData sheetId="91"/>
+      <sheetData sheetId="92"/>
+      <sheetData sheetId="93"/>
+      <sheetData sheetId="94"/>
+      <sheetData sheetId="95"/>
+      <sheetData sheetId="96"/>
+      <sheetData sheetId="97"/>
+      <sheetData sheetId="98"/>
+      <sheetData sheetId="99"/>
+      <sheetData sheetId="100"/>
+      <sheetData sheetId="101"/>
+      <sheetData sheetId="102"/>
+      <sheetData sheetId="103"/>
+      <sheetData sheetId="104"/>
+      <sheetData sheetId="105"/>
+      <sheetData sheetId="106"/>
+      <sheetData sheetId="107"/>
+      <sheetData sheetId="108"/>
+      <sheetData sheetId="109"/>
+      <sheetData sheetId="110"/>
+      <sheetData sheetId="111"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6488,1170 +5190,178 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="9" style="1"/>
-    <col min="7" max="9" width="9" style="38"/>
-    <col min="10" max="10" width="10.25" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>8</v>
+    <row r="1" spans="1:3" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="47" t="s">
+      <c r="C1" s="47" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="21" t="s">
+      <c r="B3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="36">
-        <v>0.255</v>
-      </c>
-      <c r="H2" s="36">
-        <f>G2</f>
-        <v>0.255</v>
-      </c>
-      <c r="I2" s="36">
-        <f>G2</f>
-        <v>0.255</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="36">
-        <v>0</v>
-      </c>
-      <c r="H3" s="36">
-        <f t="shared" ref="H3:H37" si="0">G3</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="36">
-        <f t="shared" ref="I3:I37" si="1">G3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="21" t="s">
+      <c r="C8" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="36">
-        <v>0</v>
-      </c>
-      <c r="H4" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="37">
-        <v>0.32100000000000001</v>
-      </c>
-      <c r="H5" s="37">
-        <f t="shared" si="0"/>
-        <v>0.32100000000000001</v>
-      </c>
-      <c r="I5" s="37">
-        <f t="shared" si="1"/>
-        <v>0.32100000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="37">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="H6" s="37">
-        <f t="shared" si="0"/>
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="I6" s="37">
-        <f t="shared" si="1"/>
-        <v>3.2000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="37">
-        <v>0</v>
-      </c>
-      <c r="H7" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="36">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="H8" s="36">
-        <f t="shared" si="0"/>
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="I8" s="36">
-        <f t="shared" si="1"/>
-        <v>0.38900000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="36">
-        <v>8.1000000000000003E-2</v>
-      </c>
-      <c r="H9" s="36">
-        <f t="shared" si="0"/>
-        <v>8.1000000000000003E-2</v>
-      </c>
-      <c r="I9" s="36">
-        <f t="shared" si="1"/>
-        <v>8.1000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="36">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H10" s="36">
-        <f t="shared" si="0"/>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="I10" s="36">
-        <f t="shared" si="1"/>
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="37">
-        <v>0</v>
-      </c>
-      <c r="H11" s="37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="37">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="H12" s="37">
-        <f t="shared" si="0"/>
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="I12" s="37">
-        <f t="shared" si="1"/>
-        <v>1.7000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="37">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="H13" s="37">
-        <f t="shared" si="0"/>
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="I13" s="37">
-        <f t="shared" si="1"/>
-        <v>9.6000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="36">
-        <v>0</v>
-      </c>
-      <c r="H14" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="36">
-        <v>0.02</v>
-      </c>
-      <c r="H15" s="36">
-        <f t="shared" si="0"/>
-        <v>0.02</v>
-      </c>
-      <c r="I15" s="36">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="36">
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="0"/>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="1"/>
-        <v>0.13200000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="37">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H17" s="37">
-        <f t="shared" si="0"/>
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="I17" s="37">
-        <f t="shared" si="1"/>
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="37">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="H18" s="37">
-        <f t="shared" si="0"/>
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="I18" s="37">
-        <f t="shared" si="1"/>
-        <v>2.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="37">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="H19" s="37">
-        <f t="shared" si="0"/>
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="I19" s="37">
-        <f t="shared" si="1"/>
-        <v>0.14099999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="36">
-        <v>0</v>
-      </c>
-      <c r="H20" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="36">
-        <v>0</v>
-      </c>
-      <c r="H21" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="36">
-        <v>2.4E-2</v>
-      </c>
-      <c r="H22" s="36">
-        <f t="shared" si="0"/>
-        <v>2.4E-2</v>
-      </c>
-      <c r="I22" s="36">
-        <f t="shared" si="1"/>
-        <v>2.4E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" s="37">
-        <v>2E-3</v>
-      </c>
-      <c r="H23" s="37">
-        <f t="shared" si="0"/>
-        <v>2E-3</v>
-      </c>
-      <c r="I23" s="37">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="37">
-        <v>0.01</v>
-      </c>
-      <c r="H24" s="37">
-        <f t="shared" si="0"/>
-        <v>0.01</v>
-      </c>
-      <c r="I24" s="37">
-        <f t="shared" si="1"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="37">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="H25" s="37">
-        <f t="shared" si="0"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="I25" s="37">
-        <f t="shared" si="1"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G26" s="36">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="H26" s="36">
-        <f t="shared" si="0"/>
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="I26" s="36">
-        <f t="shared" si="1"/>
-        <v>4.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="36">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="H27" s="36">
-        <f t="shared" si="0"/>
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="I27" s="36">
-        <f t="shared" si="1"/>
-        <v>4.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="36">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="H28" s="36">
-        <f t="shared" si="0"/>
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="I28" s="36">
-        <f t="shared" si="1"/>
-        <v>6.9000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" s="37">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="H29" s="37">
-        <f t="shared" si="0"/>
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="I29" s="37">
-        <f t="shared" si="1"/>
-        <v>7.2999999999999995E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="G30" s="37">
-        <v>9.4E-2</v>
-      </c>
-      <c r="H30" s="37">
-        <f t="shared" si="0"/>
-        <v>9.4E-2</v>
-      </c>
-      <c r="I30" s="37">
-        <f t="shared" si="1"/>
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="37">
-        <v>0.13</v>
-      </c>
-      <c r="H31" s="37">
-        <f t="shared" si="0"/>
-        <v>0.13</v>
-      </c>
-      <c r="I31" s="37">
-        <f t="shared" si="1"/>
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="36">
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="H32" s="36">
-        <f t="shared" si="0"/>
-        <v>0.11899999999999999</v>
-      </c>
-      <c r="I32" s="36">
-        <f t="shared" si="1"/>
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G33" s="36">
-        <v>0.124</v>
-      </c>
-      <c r="H33" s="36">
-        <f t="shared" si="0"/>
-        <v>0.124</v>
-      </c>
-      <c r="I33" s="36">
-        <f t="shared" si="1"/>
-        <v>0.124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="36">
-        <v>0.15</v>
-      </c>
-      <c r="H34" s="36">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-      <c r="I34" s="36">
-        <f t="shared" si="1"/>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G35" s="37">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="H35" s="37">
-        <f t="shared" si="0"/>
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="I35" s="37">
-        <f t="shared" si="1"/>
-        <v>0.16700000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F36" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="G36" s="37">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="H36" s="37">
-        <f t="shared" si="0"/>
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="I36" s="37">
-        <f t="shared" si="1"/>
-        <v>0.16800000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G37" s="37">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="H37" s="37">
-        <f t="shared" si="0"/>
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="I37" s="37">
-        <f t="shared" si="1"/>
-        <v>0.17799999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="34"/>
+      <c r="C13" s="1" t="s">
+        <v>221</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>[1.요구량Tool_ve31.xlsm]커튼월index!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A13</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>[1.요구량Tool_ve31.xlsm]커튼월index!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B13</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
